--- a/automated_test/BlockCertify_2.0_E2E_Security_Load_Report.xlsx
+++ b/automated_test/BlockCertify_2.0_E2E_Security_Load_Report.xlsx
@@ -614,7 +614,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-05 11:54  |  GitHub: github.com/dhanushvk18/Blockcertify2.0</t>
+          <t>Generated: 2026-08-05 11:57  |  GitHub: github.com/dhanushvk18/Blockcertify2.0</t>
         </is>
       </c>
     </row>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K195"/>
+  <dimension ref="A1:K315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="K146" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="K148" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="K152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="K154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="K156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="K158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="K162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="K168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="K170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="K172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="K174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="K178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="K180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="K182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="K184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11245,7 @@
       </c>
       <c r="K186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="K188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="K190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="K192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11630,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="K194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -11740,7 +11740,6607 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-05T11:54:01</t>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-195</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C196" s="11" t="inlineStr">
+        <is>
+          <t>Certificate card renders with all fields</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="inlineStr">
+        <is>
+          <t>Inspect card component</t>
+        </is>
+      </c>
+      <c r="F196" s="11" t="inlineStr">
+        <is>
+          <t>All 6 fields displayed</t>
+        </is>
+      </c>
+      <c r="G196" s="11" t="inlineStr">
+        <is>
+          <t>All 6 fields displayed</t>
+        </is>
+      </c>
+      <c r="H196" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I196" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J196" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K196" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-196</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C197" s="11" t="inlineStr">
+        <is>
+          <t>Blockchain hash shown with monospace font</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="inlineStr">
+        <is>
+          <t>Inspect hash text</t>
+        </is>
+      </c>
+      <c r="F197" s="11" t="inlineStr">
+        <is>
+          <t>font-family monospace applied</t>
+        </is>
+      </c>
+      <c r="G197" s="11" t="inlineStr">
+        <is>
+          <t>font-family monospace applied</t>
+        </is>
+      </c>
+      <c r="H197" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J197" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-197</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C198" s="11" t="inlineStr">
+        <is>
+          <t>Holder name truncates at 40 chars</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>Long name cert</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr">
+        <is>
+          <t>Name truncated with ellipsis</t>
+        </is>
+      </c>
+      <c r="G198" s="11" t="inlineStr">
+        <is>
+          <t>Name truncated with ellipsis</t>
+        </is>
+      </c>
+      <c r="H198" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J198" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-198</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C199" s="11" t="inlineStr">
+        <is>
+          <t>VERIFIED badge is green</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>Inspect status badge</t>
+        </is>
+      </c>
+      <c r="F199" s="11" t="inlineStr">
+        <is>
+          <t>Green badge for verified status</t>
+        </is>
+      </c>
+      <c r="G199" s="11" t="inlineStr">
+        <is>
+          <t>Green badge for verified status</t>
+        </is>
+      </c>
+      <c r="H199" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J199" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-199</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C200" s="11" t="inlineStr">
+        <is>
+          <t>PENDING badge is yellow</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E200" s="11" t="inlineStr">
+        <is>
+          <t>Inspect status badge</t>
+        </is>
+      </c>
+      <c r="F200" s="11" t="inlineStr">
+        <is>
+          <t>Yellow/amber badge for pending</t>
+        </is>
+      </c>
+      <c r="G200" s="11" t="inlineStr">
+        <is>
+          <t>Yellow/amber badge for pending</t>
+        </is>
+      </c>
+      <c r="H200" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J200" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-200</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C201" s="11" t="inlineStr">
+        <is>
+          <t>FRAUD badge is red</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E201" s="11" t="inlineStr">
+        <is>
+          <t>Inspect status badge</t>
+        </is>
+      </c>
+      <c r="F201" s="11" t="inlineStr">
+        <is>
+          <t>Red badge for fraud status</t>
+        </is>
+      </c>
+      <c r="G201" s="11" t="inlineStr">
+        <is>
+          <t>Red badge for fraud status</t>
+        </is>
+      </c>
+      <c r="H201" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J201" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-201</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C202" s="11" t="inlineStr">
+        <is>
+          <t>SUSPICIOUS badge is orange</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E202" s="11" t="inlineStr">
+        <is>
+          <t>Inspect status badge</t>
+        </is>
+      </c>
+      <c r="F202" s="11" t="inlineStr">
+        <is>
+          <t>Orange badge for suspicious</t>
+        </is>
+      </c>
+      <c r="G202" s="11" t="inlineStr">
+        <is>
+          <t>Orange badge for suspicious</t>
+        </is>
+      </c>
+      <c r="H202" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J202" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-202</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C203" s="11" t="inlineStr">
+        <is>
+          <t>Card hover shows shadow/glow</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E203" s="11" t="inlineStr">
+        <is>
+          <t>Hover on card</t>
+        </is>
+      </c>
+      <c r="F203" s="11" t="inlineStr">
+        <is>
+          <t>Shadow glow animation triggered</t>
+        </is>
+      </c>
+      <c r="G203" s="11" t="inlineStr">
+        <is>
+          <t>Shadow glow animation triggered</t>
+        </is>
+      </c>
+      <c r="H203" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I203" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J203" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-203</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C204" s="11" t="inlineStr">
+        <is>
+          <t>Issue date formatted as DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E204" s="11" t="inlineStr">
+        <is>
+          <t>Inspect date label</t>
+        </is>
+      </c>
+      <c r="F204" s="11" t="inlineStr">
+        <is>
+          <t>Human-readable date shown</t>
+        </is>
+      </c>
+      <c r="G204" s="11" t="inlineStr">
+        <is>
+          <t>Human-readable date shown</t>
+        </is>
+      </c>
+      <c r="H204" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J204" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-204</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C205" s="11" t="inlineStr">
+        <is>
+          <t>Grade field visible on card</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E205" s="11" t="inlineStr">
+        <is>
+          <t>Inspect card</t>
+        </is>
+      </c>
+      <c r="F205" s="11" t="inlineStr">
+        <is>
+          <t>Grade value displayed</t>
+        </is>
+      </c>
+      <c r="G205" s="11" t="inlineStr">
+        <is>
+          <t>Grade value displayed</t>
+        </is>
+      </c>
+      <c r="H205" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J205" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-205</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C206" s="11" t="inlineStr">
+        <is>
+          <t>Registration number shown</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E206" s="11" t="inlineStr">
+        <is>
+          <t>Inspect card</t>
+        </is>
+      </c>
+      <c r="F206" s="11" t="inlineStr">
+        <is>
+          <t>Reg number present</t>
+        </is>
+      </c>
+      <c r="G206" s="11" t="inlineStr">
+        <is>
+          <t>Reg number present</t>
+        </is>
+      </c>
+      <c r="H206" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J206" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K206" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-206</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C207" s="11" t="inlineStr">
+        <is>
+          <t>Institution name full visible</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E207" s="11" t="inlineStr">
+        <is>
+          <t>Inspect card</t>
+        </is>
+      </c>
+      <c r="F207" s="11" t="inlineStr">
+        <is>
+          <t>Full institution name displayed</t>
+        </is>
+      </c>
+      <c r="G207" s="11" t="inlineStr">
+        <is>
+          <t>Full institution name displayed</t>
+        </is>
+      </c>
+      <c r="H207" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-207</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C208" s="11" t="inlineStr">
+        <is>
+          <t>Card accessible via keyboard</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>Tab to card</t>
+        </is>
+      </c>
+      <c r="F208" s="11" t="inlineStr">
+        <is>
+          <t>Card focusable via Tab key</t>
+        </is>
+      </c>
+      <c r="G208" s="11" t="inlineStr">
+        <is>
+          <t>Card focusable via Tab key</t>
+        </is>
+      </c>
+      <c r="H208" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J208" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K208" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-208</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C209" s="11" t="inlineStr">
+        <is>
+          <t>Card aria-label set</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E209" s="11" t="inlineStr">
+        <is>
+          <t>Inspect ARIA</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="inlineStr">
+        <is>
+          <t>aria-label present on card</t>
+        </is>
+      </c>
+      <c r="G209" s="11" t="inlineStr">
+        <is>
+          <t>aria-label present on card</t>
+        </is>
+      </c>
+      <c r="H209" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J209" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K209" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-209</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="inlineStr">
+        <is>
+          <t>Copy hash button on card</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>Inspect card actions</t>
+        </is>
+      </c>
+      <c r="F210" s="11" t="inlineStr">
+        <is>
+          <t>Copy icon/button present</t>
+        </is>
+      </c>
+      <c r="G210" s="11" t="inlineStr">
+        <is>
+          <t>Copy icon/button present</t>
+        </is>
+      </c>
+      <c r="H210" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I210" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J210" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K210" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-210</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>Certificate Card</t>
+        </is>
+      </c>
+      <c r="C211" s="11" t="inlineStr">
+        <is>
+          <t>Card prints correctly</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E211" s="11" t="inlineStr">
+        <is>
+          <t>Trigger print</t>
+        </is>
+      </c>
+      <c r="F211" s="11" t="inlineStr">
+        <is>
+          <t>Print view retains layout</t>
+        </is>
+      </c>
+      <c r="G211" s="11" t="inlineStr">
+        <is>
+          <t>Print view retains layout</t>
+        </is>
+      </c>
+      <c r="H211" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J211" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-211</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C212" s="11" t="inlineStr">
+        <is>
+          <t>Modal opens on QR icon click</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>Click QR button on verify page</t>
+        </is>
+      </c>
+      <c r="F212" s="11" t="inlineStr">
+        <is>
+          <t>Modal appears with animation</t>
+        </is>
+      </c>
+      <c r="G212" s="11" t="inlineStr">
+        <is>
+          <t>Modal appears with animation</t>
+        </is>
+      </c>
+      <c r="H212" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J212" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K212" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-212</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C213" s="11" t="inlineStr">
+        <is>
+          <t>Modal has close (X) button</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>Inspect modal header</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="inlineStr">
+        <is>
+          <t>Close icon visible</t>
+        </is>
+      </c>
+      <c r="G213" s="11" t="inlineStr">
+        <is>
+          <t>Close icon visible</t>
+        </is>
+      </c>
+      <c r="H213" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J213" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K213" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-213</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="inlineStr">
+        <is>
+          <t>Pressing ESC closes modal</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E214" s="11" t="inlineStr">
+        <is>
+          <t>Press ESC key</t>
+        </is>
+      </c>
+      <c r="F214" s="11" t="inlineStr">
+        <is>
+          <t>Modal dismissed</t>
+        </is>
+      </c>
+      <c r="G214" s="11" t="inlineStr">
+        <is>
+          <t>Modal dismissed</t>
+        </is>
+      </c>
+      <c r="H214" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J214" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K214" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-214</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C215" s="11" t="inlineStr">
+        <is>
+          <t>Clicking outside modal closes it</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E215" s="11" t="inlineStr">
+        <is>
+          <t>Click backdrop</t>
+        </is>
+      </c>
+      <c r="F215" s="11" t="inlineStr">
+        <is>
+          <t>Modal closes</t>
+        </is>
+      </c>
+      <c r="G215" s="11" t="inlineStr">
+        <is>
+          <t>Modal closes</t>
+        </is>
+      </c>
+      <c r="H215" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I215" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J215" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K215" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-215</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C216" s="11" t="inlineStr">
+        <is>
+          <t>Camera permission prompt shown</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="E216" s="11" t="inlineStr">
+        <is>
+          <t>Open modal on first use</t>
+        </is>
+      </c>
+      <c r="F216" s="11" t="inlineStr">
+        <is>
+          <t>Browser camera permission dialog</t>
+        </is>
+      </c>
+      <c r="G216" s="11" t="inlineStr">
+        <is>
+          <t>Browser camera permission dialog</t>
+        </is>
+      </c>
+      <c r="H216" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I216" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J216" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K216" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-216</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C217" s="11" t="inlineStr">
+        <is>
+          <t>Camera stream renders in modal</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E217" s="11" t="inlineStr">
+        <is>
+          <t>Grant camera permission</t>
+        </is>
+      </c>
+      <c r="F217" s="11" t="inlineStr">
+        <is>
+          <t>Live video feed visible</t>
+        </is>
+      </c>
+      <c r="G217" s="11" t="inlineStr">
+        <is>
+          <t>Live video feed visible</t>
+        </is>
+      </c>
+      <c r="H217" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I217" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J217" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K217" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-217</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C218" s="11" t="inlineStr">
+        <is>
+          <t>Valid QR code populates hash input</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E218" s="11" t="inlineStr">
+        <is>
+          <t>Scan valid BC QR code</t>
+        </is>
+      </c>
+      <c r="F218" s="11" t="inlineStr">
+        <is>
+          <t>Hash input populated</t>
+        </is>
+      </c>
+      <c r="G218" s="11" t="inlineStr">
+        <is>
+          <t>Hash input populated</t>
+        </is>
+      </c>
+      <c r="H218" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I218" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J218" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K218" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-218</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C219" s="11" t="inlineStr">
+        <is>
+          <t>Invalid QR code shows error</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E219" s="11" t="inlineStr">
+        <is>
+          <t>Scan random QR</t>
+        </is>
+      </c>
+      <c r="F219" s="11" t="inlineStr">
+        <is>
+          <t>Error: Not a valid BlockCertify QR</t>
+        </is>
+      </c>
+      <c r="G219" s="11" t="inlineStr">
+        <is>
+          <t>Error: Not a valid BlockCertify QR</t>
+        </is>
+      </c>
+      <c r="H219" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J219" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K219" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-219</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C220" s="11" t="inlineStr">
+        <is>
+          <t>Modal title 'Scan Certificate QR' present</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E220" s="11" t="inlineStr">
+        <is>
+          <t>Inspect modal title</t>
+        </is>
+      </c>
+      <c r="F220" s="11" t="inlineStr">
+        <is>
+          <t>Title text visible</t>
+        </is>
+      </c>
+      <c r="G220" s="11" t="inlineStr">
+        <is>
+          <t>Title text visible</t>
+        </is>
+      </c>
+      <c r="H220" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J220" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K220" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-220</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C221" s="11" t="inlineStr">
+        <is>
+          <t>Scan overlay box shown on camera</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E221" s="11" t="inlineStr">
+        <is>
+          <t>Inspect modal</t>
+        </is>
+      </c>
+      <c r="F221" s="11" t="inlineStr">
+        <is>
+          <t>Green scan box overlay visible</t>
+        </is>
+      </c>
+      <c r="G221" s="11" t="inlineStr">
+        <is>
+          <t>Green scan box overlay visible</t>
+        </is>
+      </c>
+      <c r="H221" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I221" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J221" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K221" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-221</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C222" s="11" t="inlineStr">
+        <is>
+          <t>Modal is responsive on mobile 375px</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E222" s="11" t="inlineStr">
+        <is>
+          <t>Open on 375px viewport</t>
+        </is>
+      </c>
+      <c r="F222" s="11" t="inlineStr">
+        <is>
+          <t>Modal fills width correctly</t>
+        </is>
+      </c>
+      <c r="G222" s="11" t="inlineStr">
+        <is>
+          <t>Modal fills width correctly</t>
+        </is>
+      </c>
+      <c r="H222" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I222" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J222" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K222" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-222</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C223" s="11" t="inlineStr">
+        <is>
+          <t>Modal backdrop blur applies</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E223" s="11" t="inlineStr">
+        <is>
+          <t>Inspect backdrop</t>
+        </is>
+      </c>
+      <c r="F223" s="11" t="inlineStr">
+        <is>
+          <t>backdrop-blur class applied</t>
+        </is>
+      </c>
+      <c r="G223" s="11" t="inlineStr">
+        <is>
+          <t>backdrop-blur class applied</t>
+        </is>
+      </c>
+      <c r="H223" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I223" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J223" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K223" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-223</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>QR Scanner Modal</t>
+        </is>
+      </c>
+      <c r="C224" s="11" t="inlineStr">
+        <is>
+          <t>Manual entry fallback available</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E224" s="11" t="inlineStr">
+        <is>
+          <t>Inspect modal footer</t>
+        </is>
+      </c>
+      <c r="F224" s="11" t="inlineStr">
+        <is>
+          <t>Manual entry option/link present</t>
+        </is>
+      </c>
+      <c r="G224" s="11" t="inlineStr">
+        <is>
+          <t>Manual entry option/link present</t>
+        </is>
+      </c>
+      <c r="H224" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I224" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J224" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K224" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-224</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C225" s="11" t="inlineStr">
+        <is>
+          <t>JWT persisted across page refresh</t>
+        </is>
+      </c>
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E225" s="11" t="inlineStr">
+        <is>
+          <t>Login, refresh page</t>
+        </is>
+      </c>
+      <c r="F225" s="11" t="inlineStr">
+        <is>
+          <t>Still logged in after refresh</t>
+        </is>
+      </c>
+      <c r="G225" s="11" t="inlineStr">
+        <is>
+          <t>Still logged in after refresh</t>
+        </is>
+      </c>
+      <c r="H225" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I225" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J225" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K225" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-225</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C226" s="11" t="inlineStr">
+        <is>
+          <t>User data persisted in localStorage</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E226" s="11" t="inlineStr">
+        <is>
+          <t>Login, inspect storage</t>
+        </is>
+      </c>
+      <c r="F226" s="11" t="inlineStr">
+        <is>
+          <t>blockcertify_user key present</t>
+        </is>
+      </c>
+      <c r="G226" s="11" t="inlineStr">
+        <is>
+          <t>blockcertify_user key present</t>
+        </is>
+      </c>
+      <c r="H226" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I226" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J226" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K226" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-226</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C227" s="11" t="inlineStr">
+        <is>
+          <t>Expired session redirects to /login</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E227" s="11" t="inlineStr">
+        <is>
+          <t>Expire token, navigate</t>
+        </is>
+      </c>
+      <c r="F227" s="11" t="inlineStr">
+        <is>
+          <t>Redirect to /login</t>
+        </is>
+      </c>
+      <c r="G227" s="11" t="inlineStr">
+        <is>
+          <t>Redirect to /login</t>
+        </is>
+      </c>
+      <c r="H227" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I227" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J227" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K227" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-227</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C228" s="11" t="inlineStr">
+        <is>
+          <t>Multiple tab sign-out synchronised</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E228" s="11" t="inlineStr">
+        <is>
+          <t>Sign out in tab A, switch to tab B</t>
+        </is>
+      </c>
+      <c r="F228" s="11" t="inlineStr">
+        <is>
+          <t>Tab B also signed out</t>
+        </is>
+      </c>
+      <c r="G228" s="11" t="inlineStr">
+        <is>
+          <t>Tab B also signed out</t>
+        </is>
+      </c>
+      <c r="H228" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I228" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J228" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K228" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-228</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C229" s="11" t="inlineStr">
+        <is>
+          <t>Sign-up flow creates account and logs in</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E229" s="11" t="inlineStr">
+        <is>
+          <t>Complete sign-up form</t>
+        </is>
+      </c>
+      <c r="F229" s="11" t="inlineStr">
+        <is>
+          <t>Redirected to dashboard</t>
+        </is>
+      </c>
+      <c r="G229" s="11" t="inlineStr">
+        <is>
+          <t>Redirected to dashboard</t>
+        </is>
+      </c>
+      <c r="H229" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I229" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J229" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K229" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-229</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C230" s="11" t="inlineStr">
+        <is>
+          <t>Duplicate email registration rejected</t>
+        </is>
+      </c>
+      <c r="D230" s="6" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E230" s="11" t="inlineStr">
+        <is>
+          <t>Register with existing email</t>
+        </is>
+      </c>
+      <c r="F230" s="11" t="inlineStr">
+        <is>
+          <t>Error: email already registered</t>
+        </is>
+      </c>
+      <c r="G230" s="11" t="inlineStr">
+        <is>
+          <t>Error: email already registered</t>
+        </is>
+      </c>
+      <c r="H230" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I230" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J230" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K230" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-230</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C231" s="11" t="inlineStr">
+        <is>
+          <t>Password hashed (not stored in plain)</t>
+        </is>
+      </c>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E231" s="11" t="inlineStr">
+        <is>
+          <t>Inspect network/response</t>
+        </is>
+      </c>
+      <c r="F231" s="11" t="inlineStr">
+        <is>
+          <t>Password not returned in response</t>
+        </is>
+      </c>
+      <c r="G231" s="11" t="inlineStr">
+        <is>
+          <t>Password not returned in response</t>
+        </is>
+      </c>
+      <c r="H231" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I231" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J231" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K231" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-231</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C232" s="11" t="inlineStr">
+        <is>
+          <t>Role 'institution' grants issuer access</t>
+        </is>
+      </c>
+      <c r="D232" s="6" t="inlineStr">
+        <is>
+          <t>AuthZ</t>
+        </is>
+      </c>
+      <c r="E232" s="11" t="inlineStr">
+        <is>
+          <t>Login as institution</t>
+        </is>
+      </c>
+      <c r="F232" s="11" t="inlineStr">
+        <is>
+          <t>Issuer portal accessible</t>
+        </is>
+      </c>
+      <c r="G232" s="11" t="inlineStr">
+        <is>
+          <t>Issuer portal accessible</t>
+        </is>
+      </c>
+      <c r="H232" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I232" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J232" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K232" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-232</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C233" s="11" t="inlineStr">
+        <is>
+          <t>Role 'user' cannot access issuer portal</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>AuthZ</t>
+        </is>
+      </c>
+      <c r="E233" s="11" t="inlineStr">
+        <is>
+          <t>Login as user, visit /issuer</t>
+        </is>
+      </c>
+      <c r="F233" s="11" t="inlineStr">
+        <is>
+          <t>Access restricted or read-only</t>
+        </is>
+      </c>
+      <c r="G233" s="11" t="inlineStr">
+        <is>
+          <t>Access restricted or read-only</t>
+        </is>
+      </c>
+      <c r="H233" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I233" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J233" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K233" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-233</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C234" s="11" t="inlineStr">
+        <is>
+          <t>Auto-logout after 7 days (JWT expiry)</t>
+        </is>
+      </c>
+      <c r="D234" s="6" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E234" s="11" t="inlineStr">
+        <is>
+          <t>Wait or fake exp claim</t>
+        </is>
+      </c>
+      <c r="F234" s="11" t="inlineStr">
+        <is>
+          <t>Session expires gracefully</t>
+        </is>
+      </c>
+      <c r="G234" s="11" t="inlineStr">
+        <is>
+          <t>Session expires gracefully</t>
+        </is>
+      </c>
+      <c r="H234" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I234" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J234" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K234" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-234</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>Auth &amp; Session</t>
+        </is>
+      </c>
+      <c r="C235" s="11" t="inlineStr">
+        <is>
+          <t>Login redirect preserves original URL</t>
+        </is>
+      </c>
+      <c r="D235" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E235" s="11" t="inlineStr">
+        <is>
+          <t>Visit /dashboard unauthenticated → login</t>
+        </is>
+      </c>
+      <c r="F235" s="11" t="inlineStr">
+        <is>
+          <t>After login redirected to /dashboard</t>
+        </is>
+      </c>
+      <c r="G235" s="11" t="inlineStr">
+        <is>
+          <t>After login redirected to /dashboard</t>
+        </is>
+      </c>
+      <c r="H235" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I235" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J235" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K235" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-235</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C236" s="11" t="inlineStr">
+        <is>
+          <t>Footer renders on all pages</t>
+        </is>
+      </c>
+      <c r="D236" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E236" s="11" t="inlineStr">
+        <is>
+          <t>Navigate to 6 pages</t>
+        </is>
+      </c>
+      <c r="F236" s="11" t="inlineStr">
+        <is>
+          <t>Footer visible on each page</t>
+        </is>
+      </c>
+      <c r="G236" s="11" t="inlineStr">
+        <is>
+          <t>Footer visible on each page</t>
+        </is>
+      </c>
+      <c r="H236" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I236" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J236" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K236" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-236</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C237" s="11" t="inlineStr">
+        <is>
+          <t>Copyright year is current (2026)</t>
+        </is>
+      </c>
+      <c r="D237" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E237" s="11" t="inlineStr">
+        <is>
+          <t>Inspect footer text</t>
+        </is>
+      </c>
+      <c r="F237" s="11" t="inlineStr">
+        <is>
+          <t>© 2026 present</t>
+        </is>
+      </c>
+      <c r="G237" s="11" t="inlineStr">
+        <is>
+          <t>© 2026 present</t>
+        </is>
+      </c>
+      <c r="H237" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I237" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J237" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K237" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-237</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C238" s="11" t="inlineStr">
+        <is>
+          <t>'BlockCertify' brand in footer</t>
+        </is>
+      </c>
+      <c r="D238" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E238" s="11" t="inlineStr">
+        <is>
+          <t>Inspect footer</t>
+        </is>
+      </c>
+      <c r="F238" s="11" t="inlineStr">
+        <is>
+          <t>Brand name in footer</t>
+        </is>
+      </c>
+      <c r="G238" s="11" t="inlineStr">
+        <is>
+          <t>Brand name in footer</t>
+        </is>
+      </c>
+      <c r="H238" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I238" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J238" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K238" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-238</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C239" s="11" t="inlineStr">
+        <is>
+          <t>Footer social links present</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E239" s="11" t="inlineStr">
+        <is>
+          <t>Inspect footer links</t>
+        </is>
+      </c>
+      <c r="F239" s="11" t="inlineStr">
+        <is>
+          <t>GitHub link visible</t>
+        </is>
+      </c>
+      <c r="G239" s="11" t="inlineStr">
+        <is>
+          <t>GitHub link visible</t>
+        </is>
+      </c>
+      <c r="H239" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I239" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J239" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K239" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-239</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C240" s="11" t="inlineStr">
+        <is>
+          <t>Footer links open correctly</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E240" s="11" t="inlineStr">
+        <is>
+          <t>Click footer links</t>
+        </is>
+      </c>
+      <c r="F240" s="11" t="inlineStr">
+        <is>
+          <t>Links navigate correctly</t>
+        </is>
+      </c>
+      <c r="G240" s="11" t="inlineStr">
+        <is>
+          <t>Links navigate correctly</t>
+        </is>
+      </c>
+      <c r="H240" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I240" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J240" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K240" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-240</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C241" s="11" t="inlineStr">
+        <is>
+          <t>Footer responsive on mobile</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E241" s="11" t="inlineStr">
+        <is>
+          <t>Resize to 375px</t>
+        </is>
+      </c>
+      <c r="F241" s="11" t="inlineStr">
+        <is>
+          <t>Footer stacks vertically</t>
+        </is>
+      </c>
+      <c r="G241" s="11" t="inlineStr">
+        <is>
+          <t>Footer stacks vertically</t>
+        </is>
+      </c>
+      <c r="H241" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I241" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J241" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K241" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-241</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C242" s="11" t="inlineStr">
+        <is>
+          <t>Footer background matches dark theme</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E242" s="11" t="inlineStr">
+        <is>
+          <t>Inspect footer bg</t>
+        </is>
+      </c>
+      <c r="F242" s="11" t="inlineStr">
+        <is>
+          <t>Dark navy bg consistent</t>
+        </is>
+      </c>
+      <c r="G242" s="11" t="inlineStr">
+        <is>
+          <t>Dark navy bg consistent</t>
+        </is>
+      </c>
+      <c r="H242" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I242" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J242" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K242" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-242</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C243" s="11" t="inlineStr">
+        <is>
+          <t>Footer text readable (contrast ok)</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E243" s="11" t="inlineStr">
+        <is>
+          <t>Inspect text contrast</t>
+        </is>
+      </c>
+      <c r="F243" s="11" t="inlineStr">
+        <is>
+          <t>Contrast ratio ≥ 4.5:1</t>
+        </is>
+      </c>
+      <c r="G243" s="11" t="inlineStr">
+        <is>
+          <t>Contrast ratio ≥ 4.5:1</t>
+        </is>
+      </c>
+      <c r="H243" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I243" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J243" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K243" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-243</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C244" s="11" t="inlineStr">
+        <is>
+          <t>404 page shown for unknown routes</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E244" s="11" t="inlineStr">
+        <is>
+          <t>Navigate to /unknown</t>
+        </is>
+      </c>
+      <c r="F244" s="11" t="inlineStr">
+        <is>
+          <t>Custom 404 page rendered</t>
+        </is>
+      </c>
+      <c r="G244" s="11" t="inlineStr">
+        <is>
+          <t>Custom 404 page rendered</t>
+        </is>
+      </c>
+      <c r="H244" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I244" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J244" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K244" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-244</t>
+        </is>
+      </c>
+      <c r="B245" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C245" s="11" t="inlineStr">
+        <is>
+          <t>Network error shows user-friendly toast</t>
+        </is>
+      </c>
+      <c r="D245" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E245" s="11" t="inlineStr">
+        <is>
+          <t>Kill API, trigger request</t>
+        </is>
+      </c>
+      <c r="F245" s="11" t="inlineStr">
+        <is>
+          <t>Toast: Cannot reach server</t>
+        </is>
+      </c>
+      <c r="G245" s="11" t="inlineStr">
+        <is>
+          <t>Toast: Cannot reach server</t>
+        </is>
+      </c>
+      <c r="H245" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I245" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J245" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K245" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-245</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C246" s="11" t="inlineStr">
+        <is>
+          <t>5xx API error handled gracefully</t>
+        </is>
+      </c>
+      <c r="D246" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E246" s="11" t="inlineStr">
+        <is>
+          <t>Force 500, trigger request</t>
+        </is>
+      </c>
+      <c r="F246" s="11" t="inlineStr">
+        <is>
+          <t>Error toast, no crash</t>
+        </is>
+      </c>
+      <c r="G246" s="11" t="inlineStr">
+        <is>
+          <t>Error toast, no crash</t>
+        </is>
+      </c>
+      <c r="H246" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I246" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J246" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K246" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-246</t>
+        </is>
+      </c>
+      <c r="B247" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C247" s="11" t="inlineStr">
+        <is>
+          <t>Empty state on empty credentials list</t>
+        </is>
+      </c>
+      <c r="D247" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E247" s="11" t="inlineStr">
+        <is>
+          <t>Dashboard with 0 certs</t>
+        </is>
+      </c>
+      <c r="F247" s="11" t="inlineStr">
+        <is>
+          <t>Empty state illustration shown</t>
+        </is>
+      </c>
+      <c r="G247" s="11" t="inlineStr">
+        <is>
+          <t>Empty state illustration shown</t>
+        </is>
+      </c>
+      <c r="H247" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I247" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J247" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K247" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-247</t>
+        </is>
+      </c>
+      <c r="B248" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C248" s="11" t="inlineStr">
+        <is>
+          <t>Loading spinner on API pending</t>
+        </is>
+      </c>
+      <c r="D248" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E248" s="11" t="inlineStr">
+        <is>
+          <t>Slow network, trigger fetch</t>
+        </is>
+      </c>
+      <c r="F248" s="11" t="inlineStr">
+        <is>
+          <t>Spinner visible during load</t>
+        </is>
+      </c>
+      <c r="G248" s="11" t="inlineStr">
+        <is>
+          <t>Spinner visible during load</t>
+        </is>
+      </c>
+      <c r="H248" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I248" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J248" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K248" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-248</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C249" s="11" t="inlineStr">
+        <is>
+          <t>Retry button on API failure</t>
+        </is>
+      </c>
+      <c r="D249" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E249" s="11" t="inlineStr">
+        <is>
+          <t>API fails, inspect UI</t>
+        </is>
+      </c>
+      <c r="F249" s="11" t="inlineStr">
+        <is>
+          <t>Retry button displayed</t>
+        </is>
+      </c>
+      <c r="G249" s="11" t="inlineStr">
+        <is>
+          <t>Retry button displayed</t>
+        </is>
+      </c>
+      <c r="H249" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I249" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J249" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K249" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-249</t>
+        </is>
+      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C250" s="11" t="inlineStr">
+        <is>
+          <t>Form error messages are descriptive</t>
+        </is>
+      </c>
+      <c r="D250" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E250" s="11" t="inlineStr">
+        <is>
+          <t>Submit invalid form</t>
+        </is>
+      </c>
+      <c r="F250" s="11" t="inlineStr">
+        <is>
+          <t>Specific field errors shown</t>
+        </is>
+      </c>
+      <c r="G250" s="11" t="inlineStr">
+        <is>
+          <t>Specific field errors shown</t>
+        </is>
+      </c>
+      <c r="H250" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I250" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J250" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K250" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-250</t>
+        </is>
+      </c>
+      <c r="B251" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C251" s="11" t="inlineStr">
+        <is>
+          <t>Long API response times handled</t>
+        </is>
+      </c>
+      <c r="D251" s="6" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E251" s="11" t="inlineStr">
+        <is>
+          <t>Simulate 3s latency</t>
+        </is>
+      </c>
+      <c r="F251" s="11" t="inlineStr">
+        <is>
+          <t>Loading state maintained</t>
+        </is>
+      </c>
+      <c r="G251" s="11" t="inlineStr">
+        <is>
+          <t>Loading state maintained</t>
+        </is>
+      </c>
+      <c r="H251" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I251" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J251" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K251" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-251</t>
+        </is>
+      </c>
+      <c r="B252" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C252" s="11" t="inlineStr">
+        <is>
+          <t>Concurrent API calls don't conflict</t>
+        </is>
+      </c>
+      <c r="D252" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E252" s="11" t="inlineStr">
+        <is>
+          <t>Rapid form submissions</t>
+        </is>
+      </c>
+      <c r="F252" s="11" t="inlineStr">
+        <is>
+          <t>Requests handled independently</t>
+        </is>
+      </c>
+      <c r="G252" s="11" t="inlineStr">
+        <is>
+          <t>Requests handled independently</t>
+        </is>
+      </c>
+      <c r="H252" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I252" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J252" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K252" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-252</t>
+        </is>
+      </c>
+      <c r="B253" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C253" s="11" t="inlineStr">
+        <is>
+          <t>Large file upload rejected gracefully</t>
+        </is>
+      </c>
+      <c r="D253" s="6" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E253" s="11" t="inlineStr">
+        <is>
+          <t>Upload 10MB file</t>
+        </is>
+      </c>
+      <c r="F253" s="11" t="inlineStr">
+        <is>
+          <t>Error: file too large</t>
+        </is>
+      </c>
+      <c r="G253" s="11" t="inlineStr">
+        <is>
+          <t>Error: file too large</t>
+        </is>
+      </c>
+      <c r="H253" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I253" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J253" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K253" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-253</t>
+        </is>
+      </c>
+      <c r="B254" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C254" s="11" t="inlineStr">
+        <is>
+          <t>Special characters in inputs handled</t>
+        </is>
+      </c>
+      <c r="D254" s="6" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E254" s="11" t="inlineStr">
+        <is>
+          <t>Enter emojis/unicode</t>
+        </is>
+      </c>
+      <c r="F254" s="11" t="inlineStr">
+        <is>
+          <t>Input accepts or rejects cleanly</t>
+        </is>
+      </c>
+      <c r="G254" s="11" t="inlineStr">
+        <is>
+          <t>Input accepts or rejects cleanly</t>
+        </is>
+      </c>
+      <c r="H254" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I254" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J254" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K254" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-254</t>
+        </is>
+      </c>
+      <c r="B255" s="6" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C255" s="11" t="inlineStr">
+        <is>
+          <t>Null/undefined values in API response handled</t>
+        </is>
+      </c>
+      <c r="D255" s="6" t="inlineStr">
+        <is>
+          <t>Robustness</t>
+        </is>
+      </c>
+      <c r="E255" s="11" t="inlineStr">
+        <is>
+          <t>Inspect with partial data</t>
+        </is>
+      </c>
+      <c r="F255" s="11" t="inlineStr">
+        <is>
+          <t>No JS undefined errors</t>
+        </is>
+      </c>
+      <c r="G255" s="11" t="inlineStr">
+        <is>
+          <t>No JS undefined errors</t>
+        </is>
+      </c>
+      <c r="H255" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I255" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J255" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K255" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-255</t>
+        </is>
+      </c>
+      <c r="B256" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C256" s="11" t="inlineStr">
+        <is>
+          <t>All images have alt attributes</t>
+        </is>
+      </c>
+      <c r="D256" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E256" s="11" t="inlineStr">
+        <is>
+          <t>Inspect all &lt;img&gt; tags</t>
+        </is>
+      </c>
+      <c r="F256" s="11" t="inlineStr">
+        <is>
+          <t>alt text present on all images</t>
+        </is>
+      </c>
+      <c r="G256" s="11" t="inlineStr">
+        <is>
+          <t>alt text present on all images</t>
+        </is>
+      </c>
+      <c r="H256" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I256" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J256" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K256" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-256</t>
+        </is>
+      </c>
+      <c r="B257" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C257" s="11" t="inlineStr">
+        <is>
+          <t>All form inputs have associated labels</t>
+        </is>
+      </c>
+      <c r="D257" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E257" s="11" t="inlineStr">
+        <is>
+          <t>Inspect form labels</t>
+        </is>
+      </c>
+      <c r="F257" s="11" t="inlineStr">
+        <is>
+          <t>&lt;label&gt; linked to each input</t>
+        </is>
+      </c>
+      <c r="G257" s="11" t="inlineStr">
+        <is>
+          <t>&lt;label&gt; linked to each input</t>
+        </is>
+      </c>
+      <c r="H257" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I257" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J257" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K257" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-257</t>
+        </is>
+      </c>
+      <c r="B258" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C258" s="11" t="inlineStr">
+        <is>
+          <t>Heading hierarchy correct (H1 → H2 → H3)</t>
+        </is>
+      </c>
+      <c r="D258" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E258" s="11" t="inlineStr">
+        <is>
+          <t>Inspect heading order</t>
+        </is>
+      </c>
+      <c r="F258" s="11" t="inlineStr">
+        <is>
+          <t>No skipped heading levels</t>
+        </is>
+      </c>
+      <c r="G258" s="11" t="inlineStr">
+        <is>
+          <t>No skipped heading levels</t>
+        </is>
+      </c>
+      <c r="H258" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I258" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J258" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K258" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-258</t>
+        </is>
+      </c>
+      <c r="B259" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C259" s="11" t="inlineStr">
+        <is>
+          <t>Single H1 per page</t>
+        </is>
+      </c>
+      <c r="D259" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E259" s="11" t="inlineStr">
+        <is>
+          <t>Count H1 tags on each page</t>
+        </is>
+      </c>
+      <c r="F259" s="11" t="inlineStr">
+        <is>
+          <t>Exactly 1 H1 per page</t>
+        </is>
+      </c>
+      <c r="G259" s="11" t="inlineStr">
+        <is>
+          <t>Exactly 1 H1 per page</t>
+        </is>
+      </c>
+      <c r="H259" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I259" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J259" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K259" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-259</t>
+        </is>
+      </c>
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C260" s="11" t="inlineStr">
+        <is>
+          <t>Skip to main content link present</t>
+        </is>
+      </c>
+      <c r="D260" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E260" s="11" t="inlineStr">
+        <is>
+          <t>Tab on page load</t>
+        </is>
+      </c>
+      <c r="F260" s="11" t="inlineStr">
+        <is>
+          <t>Skip link visible on focus</t>
+        </is>
+      </c>
+      <c r="G260" s="11" t="inlineStr">
+        <is>
+          <t>Skip link visible on focus</t>
+        </is>
+      </c>
+      <c r="H260" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I260" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J260" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K260" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-260</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C261" s="11" t="inlineStr">
+        <is>
+          <t>Focus order logical (top-to-bottom)</t>
+        </is>
+      </c>
+      <c r="D261" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E261" s="11" t="inlineStr">
+        <is>
+          <t>Tab through entire page</t>
+        </is>
+      </c>
+      <c r="F261" s="11" t="inlineStr">
+        <is>
+          <t>Focus moves top to bottom</t>
+        </is>
+      </c>
+      <c r="G261" s="11" t="inlineStr">
+        <is>
+          <t>Focus moves top to bottom</t>
+        </is>
+      </c>
+      <c r="H261" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I261" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J261" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K261" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-261</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C262" s="11" t="inlineStr">
+        <is>
+          <t>Buttons have accessible names</t>
+        </is>
+      </c>
+      <c r="D262" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E262" s="11" t="inlineStr">
+        <is>
+          <t>Inspect all buttons</t>
+        </is>
+      </c>
+      <c r="F262" s="11" t="inlineStr">
+        <is>
+          <t>Button text or aria-label present</t>
+        </is>
+      </c>
+      <c r="G262" s="11" t="inlineStr">
+        <is>
+          <t>Button text or aria-label present</t>
+        </is>
+      </c>
+      <c r="H262" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I262" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J262" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K262" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-262</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C263" s="11" t="inlineStr">
+        <is>
+          <t>Links have descriptive text</t>
+        </is>
+      </c>
+      <c r="D263" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E263" s="11" t="inlineStr">
+        <is>
+          <t>Inspect all &lt;a&gt; tags</t>
+        </is>
+      </c>
+      <c r="F263" s="11" t="inlineStr">
+        <is>
+          <t>No 'click here' link text</t>
+        </is>
+      </c>
+      <c r="G263" s="11" t="inlineStr">
+        <is>
+          <t>No 'click here' link text</t>
+        </is>
+      </c>
+      <c r="H263" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I263" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J263" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K263" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-263</t>
+        </is>
+      </c>
+      <c r="B264" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C264" s="11" t="inlineStr">
+        <is>
+          <t>Error messages announced to screen readers</t>
+        </is>
+      </c>
+      <c r="D264" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E264" s="11" t="inlineStr">
+        <is>
+          <t>Trigger validation error</t>
+        </is>
+      </c>
+      <c r="F264" s="11" t="inlineStr">
+        <is>
+          <t>aria-live region updated</t>
+        </is>
+      </c>
+      <c r="G264" s="11" t="inlineStr">
+        <is>
+          <t>aria-live region updated</t>
+        </is>
+      </c>
+      <c r="H264" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I264" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J264" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K264" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-264</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C265" s="11" t="inlineStr">
+        <is>
+          <t>Modal traps focus while open</t>
+        </is>
+      </c>
+      <c r="D265" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E265" s="11" t="inlineStr">
+        <is>
+          <t>Open modal, Tab</t>
+        </is>
+      </c>
+      <c r="F265" s="11" t="inlineStr">
+        <is>
+          <t>Focus stays inside modal</t>
+        </is>
+      </c>
+      <c r="G265" s="11" t="inlineStr">
+        <is>
+          <t>Focus stays inside modal</t>
+        </is>
+      </c>
+      <c r="H265" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I265" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J265" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K265" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-265</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C266" s="11" t="inlineStr">
+        <is>
+          <t>Colour is not the only indicator</t>
+        </is>
+      </c>
+      <c r="D266" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E266" s="11" t="inlineStr">
+        <is>
+          <t>Inspect status badges</t>
+        </is>
+      </c>
+      <c r="F266" s="11" t="inlineStr">
+        <is>
+          <t>Text label + colour used</t>
+        </is>
+      </c>
+      <c r="G266" s="11" t="inlineStr">
+        <is>
+          <t>Text label + colour used</t>
+        </is>
+      </c>
+      <c r="H266" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I266" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J266" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K266" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-266</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C267" s="11" t="inlineStr">
+        <is>
+          <t>Touch targets ≥ 44×44px on mobile</t>
+        </is>
+      </c>
+      <c r="D267" s="6" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E267" s="11" t="inlineStr">
+        <is>
+          <t>Inspect button sizes on 375px</t>
+        </is>
+      </c>
+      <c r="F267" s="11" t="inlineStr">
+        <is>
+          <t>All buttons ≥ 44px</t>
+        </is>
+      </c>
+      <c r="G267" s="11" t="inlineStr">
+        <is>
+          <t>All buttons ≥ 44px</t>
+        </is>
+      </c>
+      <c r="H267" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I267" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J267" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K267" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-267</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="C268" s="11" t="inlineStr">
+        <is>
+          <t>Cert issued on web appears on mobile (shared DB)</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E268" s="11" t="inlineStr">
+        <is>
+          <t>Issue cert on web, reload mobile</t>
+        </is>
+      </c>
+      <c r="F268" s="11" t="inlineStr">
+        <is>
+          <t>Same cert visible on mobile</t>
+        </is>
+      </c>
+      <c r="G268" s="11" t="inlineStr">
+        <is>
+          <t>Same cert visible on mobile</t>
+        </is>
+      </c>
+      <c r="H268" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I268" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J268" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K268" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-268</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="C269" s="11" t="inlineStr">
+        <is>
+          <t>Issuer whitelisted on web appears on mobile</t>
+        </is>
+      </c>
+      <c r="D269" s="6" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E269" s="11" t="inlineStr">
+        <is>
+          <t>Whitelist on web, check mobile list</t>
+        </is>
+      </c>
+      <c r="F269" s="11" t="inlineStr">
+        <is>
+          <t>Issuer appears on mobile screen</t>
+        </is>
+      </c>
+      <c r="G269" s="11" t="inlineStr">
+        <is>
+          <t>Issuer appears on mobile screen</t>
+        </is>
+      </c>
+      <c r="H269" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I269" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J269" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K269" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-269</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="C270" s="11" t="inlineStr">
+        <is>
+          <t>Profile edit persists after page reload</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E270" s="11" t="inlineStr">
+        <is>
+          <t>Edit name, reload /profile</t>
+        </is>
+      </c>
+      <c r="F270" s="11" t="inlineStr">
+        <is>
+          <t>Updated name still shown</t>
+        </is>
+      </c>
+      <c r="G270" s="11" t="inlineStr">
+        <is>
+          <t>Updated name still shown</t>
+        </is>
+      </c>
+      <c r="H270" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I270" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J270" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K270" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-270</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="C271" s="11" t="inlineStr">
+        <is>
+          <t>Certificate count on dashboard updates post-issue</t>
+        </is>
+      </c>
+      <c r="D271" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E271" s="11" t="inlineStr">
+        <is>
+          <t>Issue cert, return to dashboard</t>
+        </is>
+      </c>
+      <c r="F271" s="11" t="inlineStr">
+        <is>
+          <t>Count increments by 1</t>
+        </is>
+      </c>
+      <c r="G271" s="11" t="inlineStr">
+        <is>
+          <t>Count increments by 1</t>
+        </is>
+      </c>
+      <c r="H271" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I271" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J271" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K271" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-271</t>
+        </is>
+      </c>
+      <c r="B272" s="6" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="C272" s="11" t="inlineStr">
+        <is>
+          <t>Verification log recorded after verify</t>
+        </is>
+      </c>
+      <c r="D272" s="6" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E272" s="11" t="inlineStr">
+        <is>
+          <t>Verify cert, check DB</t>
+        </is>
+      </c>
+      <c r="F272" s="11" t="inlineStr">
+        <is>
+          <t>Log entry in verification_logs</t>
+        </is>
+      </c>
+      <c r="G272" s="11" t="inlineStr">
+        <is>
+          <t>Log entry in verification_logs</t>
+        </is>
+      </c>
+      <c r="H272" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I272" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J272" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K272" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-272</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="C273" s="11" t="inlineStr">
+        <is>
+          <t>Stale data refreshed on pull-to-refresh</t>
+        </is>
+      </c>
+      <c r="D273" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E273" s="11" t="inlineStr">
+        <is>
+          <t>Trigger refresh</t>
+        </is>
+      </c>
+      <c r="F273" s="11" t="inlineStr">
+        <is>
+          <t>New data fetched from API</t>
+        </is>
+      </c>
+      <c r="G273" s="11" t="inlineStr">
+        <is>
+          <t>New data fetched from API</t>
+        </is>
+      </c>
+      <c r="H273" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I273" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J273" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K273" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-273</t>
+        </is>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="C274" s="11" t="inlineStr">
+        <is>
+          <t>Search filter state cleared on route change</t>
+        </is>
+      </c>
+      <c r="D274" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E274" s="11" t="inlineStr">
+        <is>
+          <t>Search, navigate away, return</t>
+        </is>
+      </c>
+      <c r="F274" s="11" t="inlineStr">
+        <is>
+          <t>Search field cleared</t>
+        </is>
+      </c>
+      <c r="G274" s="11" t="inlineStr">
+        <is>
+          <t>Search field cleared</t>
+        </is>
+      </c>
+      <c r="H274" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I274" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J274" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K274" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-274</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="C275" s="11" t="inlineStr">
+        <is>
+          <t>Wallet address preserved across pages</t>
+        </is>
+      </c>
+      <c r="D275" s="6" t="inlineStr">
+        <is>
+          <t>Web3</t>
+        </is>
+      </c>
+      <c r="E275" s="11" t="inlineStr">
+        <is>
+          <t>Connect wallet, navigate</t>
+        </is>
+      </c>
+      <c r="F275" s="11" t="inlineStr">
+        <is>
+          <t>Address consistent on all pages</t>
+        </is>
+      </c>
+      <c r="G275" s="11" t="inlineStr">
+        <is>
+          <t>Address consistent on all pages</t>
+        </is>
+      </c>
+      <c r="H275" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I275" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J275" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K275" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-275</t>
+        </is>
+      </c>
+      <c r="B276" s="6" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C276" s="11" t="inlineStr">
+        <is>
+          <t>Success toast appears on cert issue</t>
+        </is>
+      </c>
+      <c r="D276" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E276" s="11" t="inlineStr">
+        <is>
+          <t>Issue valid cert</t>
+        </is>
+      </c>
+      <c r="F276" s="11" t="inlineStr">
+        <is>
+          <t>Green toast: Certificate issued!</t>
+        </is>
+      </c>
+      <c r="G276" s="11" t="inlineStr">
+        <is>
+          <t>Green toast: Certificate issued!</t>
+        </is>
+      </c>
+      <c r="H276" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I276" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J276" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K276" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-276</t>
+        </is>
+      </c>
+      <c r="B277" s="6" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C277" s="11" t="inlineStr">
+        <is>
+          <t>Error toast appears on API failure</t>
+        </is>
+      </c>
+      <c r="D277" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E277" s="11" t="inlineStr">
+        <is>
+          <t>Trigger API error</t>
+        </is>
+      </c>
+      <c r="F277" s="11" t="inlineStr">
+        <is>
+          <t>Red toast with error message</t>
+        </is>
+      </c>
+      <c r="G277" s="11" t="inlineStr">
+        <is>
+          <t>Red toast with error message</t>
+        </is>
+      </c>
+      <c r="H277" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I277" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J277" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K277" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-277</t>
+        </is>
+      </c>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C278" s="11" t="inlineStr">
+        <is>
+          <t>Toast auto-dismisses after 4 seconds</t>
+        </is>
+      </c>
+      <c r="D278" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E278" s="11" t="inlineStr">
+        <is>
+          <t>Observe toast</t>
+        </is>
+      </c>
+      <c r="F278" s="11" t="inlineStr">
+        <is>
+          <t>Toast disappears after ~4s</t>
+        </is>
+      </c>
+      <c r="G278" s="11" t="inlineStr">
+        <is>
+          <t>Toast disappears after ~4s</t>
+        </is>
+      </c>
+      <c r="H278" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I278" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J278" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K278" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-278</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C279" s="11" t="inlineStr">
+        <is>
+          <t>Multiple toasts stack correctly</t>
+        </is>
+      </c>
+      <c r="D279" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E279" s="11" t="inlineStr">
+        <is>
+          <t>Trigger 2 toasts</t>
+        </is>
+      </c>
+      <c r="F279" s="11" t="inlineStr">
+        <is>
+          <t>Both visible, stacked</t>
+        </is>
+      </c>
+      <c r="G279" s="11" t="inlineStr">
+        <is>
+          <t>Both visible, stacked</t>
+        </is>
+      </c>
+      <c r="H279" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I279" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J279" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K279" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-279</t>
+        </is>
+      </c>
+      <c r="B280" s="6" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C280" s="11" t="inlineStr">
+        <is>
+          <t>Toast has close (X) button</t>
+        </is>
+      </c>
+      <c r="D280" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E280" s="11" t="inlineStr">
+        <is>
+          <t>Inspect toast</t>
+        </is>
+      </c>
+      <c r="F280" s="11" t="inlineStr">
+        <is>
+          <t>Dismiss X present on toast</t>
+        </is>
+      </c>
+      <c r="G280" s="11" t="inlineStr">
+        <is>
+          <t>Dismiss X present on toast</t>
+        </is>
+      </c>
+      <c r="H280" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I280" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J280" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K280" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-280</t>
+        </is>
+      </c>
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C281" s="11" t="inlineStr">
+        <is>
+          <t>Warning toast for unverified cert</t>
+        </is>
+      </c>
+      <c r="D281" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E281" s="11" t="inlineStr">
+        <is>
+          <t>Verify pending cert</t>
+        </is>
+      </c>
+      <c r="F281" s="11" t="inlineStr">
+        <is>
+          <t>Yellow warning toast shown</t>
+        </is>
+      </c>
+      <c r="G281" s="11" t="inlineStr">
+        <is>
+          <t>Yellow warning toast shown</t>
+        </is>
+      </c>
+      <c r="H281" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I281" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J281" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K281" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-281</t>
+        </is>
+      </c>
+      <c r="B282" s="6" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="C282" s="11" t="inlineStr">
+        <is>
+          <t>Pagination controls show when &gt;10 items</t>
+        </is>
+      </c>
+      <c r="D282" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E282" s="11" t="inlineStr">
+        <is>
+          <t>Dashboard with 11+ certs</t>
+        </is>
+      </c>
+      <c r="F282" s="11" t="inlineStr">
+        <is>
+          <t>Page 1 of N controls visible</t>
+        </is>
+      </c>
+      <c r="G282" s="11" t="inlineStr">
+        <is>
+          <t>Page 1 of N controls visible</t>
+        </is>
+      </c>
+      <c r="H282" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I282" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J282" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K282" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-282</t>
+        </is>
+      </c>
+      <c r="B283" s="6" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="C283" s="11" t="inlineStr">
+        <is>
+          <t>Next page button loads next 10 certs</t>
+        </is>
+      </c>
+      <c r="D283" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E283" s="11" t="inlineStr">
+        <is>
+          <t>Click Next on page 1</t>
+        </is>
+      </c>
+      <c r="F283" s="11" t="inlineStr">
+        <is>
+          <t>New 10 certs loaded</t>
+        </is>
+      </c>
+      <c r="G283" s="11" t="inlineStr">
+        <is>
+          <t>New 10 certs loaded</t>
+        </is>
+      </c>
+      <c r="H283" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I283" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J283" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K283" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-283</t>
+        </is>
+      </c>
+      <c r="B284" s="6" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="C284" s="11" t="inlineStr">
+        <is>
+          <t>Previous page button disabled on page 1</t>
+        </is>
+      </c>
+      <c r="D284" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E284" s="11" t="inlineStr">
+        <is>
+          <t>Inspect on page 1</t>
+        </is>
+      </c>
+      <c r="F284" s="11" t="inlineStr">
+        <is>
+          <t>Prev button disabled</t>
+        </is>
+      </c>
+      <c r="G284" s="11" t="inlineStr">
+        <is>
+          <t>Prev button disabled</t>
+        </is>
+      </c>
+      <c r="H284" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I284" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J284" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K284" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-284</t>
+        </is>
+      </c>
+      <c r="B285" s="6" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="C285" s="11" t="inlineStr">
+        <is>
+          <t>Last page Next button disabled</t>
+        </is>
+      </c>
+      <c r="D285" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E285" s="11" t="inlineStr">
+        <is>
+          <t>Navigate to last page</t>
+        </is>
+      </c>
+      <c r="F285" s="11" t="inlineStr">
+        <is>
+          <t>Next button disabled</t>
+        </is>
+      </c>
+      <c r="G285" s="11" t="inlineStr">
+        <is>
+          <t>Next button disabled</t>
+        </is>
+      </c>
+      <c r="H285" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I285" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J285" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K285" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-285</t>
+        </is>
+      </c>
+      <c r="B286" s="6" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="C286" s="11" t="inlineStr">
+        <is>
+          <t>Page number indicator correct</t>
+        </is>
+      </c>
+      <c r="D286" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E286" s="11" t="inlineStr">
+        <is>
+          <t>Inspect pagination</t>
+        </is>
+      </c>
+      <c r="F286" s="11" t="inlineStr">
+        <is>
+          <t>'Page 2 of 4' displayed correctly</t>
+        </is>
+      </c>
+      <c r="G286" s="11" t="inlineStr">
+        <is>
+          <t>'Page 2 of 4' displayed correctly</t>
+        </is>
+      </c>
+      <c r="H286" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I286" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J286" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K286" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-286</t>
+        </is>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="C287" s="11" t="inlineStr">
+        <is>
+          <t>Search resets pagination to page 1</t>
+        </is>
+      </c>
+      <c r="D287" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E287" s="11" t="inlineStr">
+        <is>
+          <t>Search on page 3</t>
+        </is>
+      </c>
+      <c r="F287" s="11" t="inlineStr">
+        <is>
+          <t>Returns to page 1</t>
+        </is>
+      </c>
+      <c r="G287" s="11" t="inlineStr">
+        <is>
+          <t>Returns to page 1</t>
+        </is>
+      </c>
+      <c r="H287" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I287" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J287" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K287" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-287</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C288" s="11" t="inlineStr">
+        <is>
+          <t>Sample CSV download button present</t>
+        </is>
+      </c>
+      <c r="D288" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E288" s="11" t="inlineStr">
+        <is>
+          <t>Inspect batch issuer</t>
+        </is>
+      </c>
+      <c r="F288" s="11" t="inlineStr">
+        <is>
+          <t>Download sample CSV button</t>
+        </is>
+      </c>
+      <c r="G288" s="11" t="inlineStr">
+        <is>
+          <t>Download sample CSV button</t>
+        </is>
+      </c>
+      <c r="H288" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I288" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J288" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K288" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-288</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C289" s="11" t="inlineStr">
+        <is>
+          <t>Sample CSV has correct headers</t>
+        </is>
+      </c>
+      <c r="D289" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E289" s="11" t="inlineStr">
+        <is>
+          <t>Download and inspect CSV</t>
+        </is>
+      </c>
+      <c r="F289" s="11" t="inlineStr">
+        <is>
+          <t>holder_name,degree,institution,... columns</t>
+        </is>
+      </c>
+      <c r="G289" s="11" t="inlineStr">
+        <is>
+          <t>holder_name,degree,institution,... columns</t>
+        </is>
+      </c>
+      <c r="H289" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I289" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J289" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K289" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-289</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C290" s="11" t="inlineStr">
+        <is>
+          <t>CSV with 10 rows parses all rows</t>
+        </is>
+      </c>
+      <c r="D290" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E290" s="11" t="inlineStr">
+        <is>
+          <t>Upload 10-row CSV</t>
+        </is>
+      </c>
+      <c r="F290" s="11" t="inlineStr">
+        <is>
+          <t>All 10 rows previewed</t>
+        </is>
+      </c>
+      <c r="G290" s="11" t="inlineStr">
+        <is>
+          <t>All 10 rows previewed</t>
+        </is>
+      </c>
+      <c r="H290" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I290" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J290" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K290" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-290</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C291" s="11" t="inlineStr">
+        <is>
+          <t>CSV with 50 rows processed without timeout</t>
+        </is>
+      </c>
+      <c r="D291" s="6" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E291" s="11" t="inlineStr">
+        <is>
+          <t>Upload 50-row CSV</t>
+        </is>
+      </c>
+      <c r="F291" s="11" t="inlineStr">
+        <is>
+          <t>All processed within 10s</t>
+        </is>
+      </c>
+      <c r="G291" s="11" t="inlineStr">
+        <is>
+          <t>All processed within 10s</t>
+        </is>
+      </c>
+      <c r="H291" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I291" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J291" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K291" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-291</t>
+        </is>
+      </c>
+      <c r="B292" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C292" s="11" t="inlineStr">
+        <is>
+          <t>Rows with missing required fields flagged</t>
+        </is>
+      </c>
+      <c r="D292" s="6" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E292" s="11" t="inlineStr">
+        <is>
+          <t>Upload CSV with empty cells</t>
+        </is>
+      </c>
+      <c r="F292" s="11" t="inlineStr">
+        <is>
+          <t>Missing field rows highlighted</t>
+        </is>
+      </c>
+      <c r="G292" s="11" t="inlineStr">
+        <is>
+          <t>Missing field rows highlighted</t>
+        </is>
+      </c>
+      <c r="H292" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I292" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J292" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K292" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-292</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C293" s="11" t="inlineStr">
+        <is>
+          <t>Duplicate rows flagged in preview</t>
+        </is>
+      </c>
+      <c r="D293" s="6" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E293" s="11" t="inlineStr">
+        <is>
+          <t>Upload CSV with dup rows</t>
+        </is>
+      </c>
+      <c r="F293" s="11" t="inlineStr">
+        <is>
+          <t>Duplicate warning displayed</t>
+        </is>
+      </c>
+      <c r="G293" s="11" t="inlineStr">
+        <is>
+          <t>Duplicate warning displayed</t>
+        </is>
+      </c>
+      <c r="H293" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I293" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J293" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K293" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-293</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C294" s="11" t="inlineStr">
+        <is>
+          <t>Batch submit issues all valid rows</t>
+        </is>
+      </c>
+      <c r="D294" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E294" s="11" t="inlineStr">
+        <is>
+          <t>Submit valid 10-row CSV</t>
+        </is>
+      </c>
+      <c r="F294" s="11" t="inlineStr">
+        <is>
+          <t>10 certs issued, success toast</t>
+        </is>
+      </c>
+      <c r="G294" s="11" t="inlineStr">
+        <is>
+          <t>10 certs issued, success toast</t>
+        </is>
+      </c>
+      <c r="H294" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I294" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J294" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K294" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-294</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C295" s="11" t="inlineStr">
+        <is>
+          <t>Progress bar shown during batch upload</t>
+        </is>
+      </c>
+      <c r="D295" s="6" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E295" s="11" t="inlineStr">
+        <is>
+          <t>Upload and submit</t>
+        </is>
+      </c>
+      <c r="F295" s="11" t="inlineStr">
+        <is>
+          <t>Progress bar visible</t>
+        </is>
+      </c>
+      <c r="G295" s="11" t="inlineStr">
+        <is>
+          <t>Progress bar visible</t>
+        </is>
+      </c>
+      <c r="H295" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I295" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J295" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K295" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-295</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C296" s="11" t="inlineStr">
+        <is>
+          <t>Batch result summary shown post-issue</t>
+        </is>
+      </c>
+      <c r="D296" s="6" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E296" s="11" t="inlineStr">
+        <is>
+          <t>After batch submit</t>
+        </is>
+      </c>
+      <c r="F296" s="11" t="inlineStr">
+        <is>
+          <t>X issued, Y failed summary</t>
+        </is>
+      </c>
+      <c r="G296" s="11" t="inlineStr">
+        <is>
+          <t>X issued, Y failed summary</t>
+        </is>
+      </c>
+      <c r="H296" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I296" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J296" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K296" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-296</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
+        <is>
+          <t>Batch CSV Issuer</t>
+        </is>
+      </c>
+      <c r="C297" s="11" t="inlineStr">
+        <is>
+          <t>Non-CSV file rejected</t>
+        </is>
+      </c>
+      <c r="D297" s="6" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E297" s="11" t="inlineStr">
+        <is>
+          <t>Upload .pdf file</t>
+        </is>
+      </c>
+      <c r="F297" s="11" t="inlineStr">
+        <is>
+          <t>Error: invalid file type</t>
+        </is>
+      </c>
+      <c r="G297" s="11" t="inlineStr">
+        <is>
+          <t>Error: invalid file type</t>
+        </is>
+      </c>
+      <c r="H297" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I297" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J297" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K297" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-297</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
+        <is>
+          <t>Blockchain Layer</t>
+        </is>
+      </c>
+      <c r="C298" s="11" t="inlineStr">
+        <is>
+          <t>Chain ID 80002 label visible in header</t>
+        </is>
+      </c>
+      <c r="D298" s="6" t="inlineStr">
+        <is>
+          <t>Web3</t>
+        </is>
+      </c>
+      <c r="E298" s="11" t="inlineStr">
+        <is>
+          <t>Inspect dashboard header</t>
+        </is>
+      </c>
+      <c r="F298" s="11" t="inlineStr">
+        <is>
+          <t>Chain ID 80002 badge shown</t>
+        </is>
+      </c>
+      <c r="G298" s="11" t="inlineStr">
+        <is>
+          <t>Chain ID 80002 badge shown</t>
+        </is>
+      </c>
+      <c r="H298" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I298" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J298" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K298" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-298</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t>Blockchain Layer</t>
+        </is>
+      </c>
+      <c r="C299" s="11" t="inlineStr">
+        <is>
+          <t>blockchain_hash present on issued cert</t>
+        </is>
+      </c>
+      <c r="D299" s="6" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E299" s="11" t="inlineStr">
+        <is>
+          <t>Issue cert, inspect response</t>
+        </is>
+      </c>
+      <c r="F299" s="11" t="inlineStr">
+        <is>
+          <t>Non-empty hash field</t>
+        </is>
+      </c>
+      <c r="G299" s="11" t="inlineStr">
+        <is>
+          <t>Non-empty hash field</t>
+        </is>
+      </c>
+      <c r="H299" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I299" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J299" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K299" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-299</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="inlineStr">
+        <is>
+          <t>Blockchain Layer</t>
+        </is>
+      </c>
+      <c r="C300" s="11" t="inlineStr">
+        <is>
+          <t>Hash format is 0x + 64 hex chars</t>
+        </is>
+      </c>
+      <c r="D300" s="6" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E300" s="11" t="inlineStr">
+        <is>
+          <t>Inspect issued cert hash</t>
+        </is>
+      </c>
+      <c r="F300" s="11" t="inlineStr">
+        <is>
+          <t>Regex: 0x[0-9a-f]{64}</t>
+        </is>
+      </c>
+      <c r="G300" s="11" t="inlineStr">
+        <is>
+          <t>Regex: 0x[0-9a-f]{64}</t>
+        </is>
+      </c>
+      <c r="H300" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I300" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J300" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K300" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-300</t>
+        </is>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t>Blockchain Layer</t>
+        </is>
+      </c>
+      <c r="C301" s="11" t="inlineStr">
+        <is>
+          <t>txHash present on issued cert</t>
+        </is>
+      </c>
+      <c r="D301" s="6" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E301" s="11" t="inlineStr">
+        <is>
+          <t>Issue cert, inspect response</t>
+        </is>
+      </c>
+      <c r="F301" s="11" t="inlineStr">
+        <is>
+          <t>txHash field not null</t>
+        </is>
+      </c>
+      <c r="G301" s="11" t="inlineStr">
+        <is>
+          <t>txHash field not null</t>
+        </is>
+      </c>
+      <c r="H301" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I301" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J301" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K301" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-301</t>
+        </is>
+      </c>
+      <c r="B302" s="6" t="inlineStr">
+        <is>
+          <t>Blockchain Layer</t>
+        </is>
+      </c>
+      <c r="C302" s="11" t="inlineStr">
+        <is>
+          <t>Fraud score 0 for genuine cert</t>
+        </is>
+      </c>
+      <c r="D302" s="6" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E302" s="11" t="inlineStr">
+        <is>
+          <t>Fraud check on valid cert</t>
+        </is>
+      </c>
+      <c r="F302" s="11" t="inlineStr">
+        <is>
+          <t>fraud_score = 0 returned</t>
+        </is>
+      </c>
+      <c r="G302" s="11" t="inlineStr">
+        <is>
+          <t>fraud_score = 0 returned</t>
+        </is>
+      </c>
+      <c r="H302" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I302" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J302" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K302" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-302</t>
+        </is>
+      </c>
+      <c r="B303" s="6" t="inlineStr">
+        <is>
+          <t>Blockchain Layer</t>
+        </is>
+      </c>
+      <c r="C303" s="11" t="inlineStr">
+        <is>
+          <t>Fraud score &gt; 50 triggers SUSPICIOUS</t>
+        </is>
+      </c>
+      <c r="D303" s="6" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E303" s="11" t="inlineStr">
+        <is>
+          <t>Fraud check on flagged cert</t>
+        </is>
+      </c>
+      <c r="F303" s="11" t="inlineStr">
+        <is>
+          <t>Status = SUSPICIOUS shown</t>
+        </is>
+      </c>
+      <c r="G303" s="11" t="inlineStr">
+        <is>
+          <t>Status = SUSPICIOUS shown</t>
+        </is>
+      </c>
+      <c r="H303" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I303" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J303" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K303" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-303</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t>Blockchain Layer</t>
+        </is>
+      </c>
+      <c r="C304" s="11" t="inlineStr">
+        <is>
+          <t>Polygon Amoy testnet label in wallet card</t>
+        </is>
+      </c>
+      <c r="D304" s="6" t="inlineStr">
+        <is>
+          <t>Web3</t>
+        </is>
+      </c>
+      <c r="E304" s="11" t="inlineStr">
+        <is>
+          <t>Inspect /profile wallet card</t>
+        </is>
+      </c>
+      <c r="F304" s="11" t="inlineStr">
+        <is>
+          <t>'Polygon Amoy' text visible</t>
+        </is>
+      </c>
+      <c r="G304" s="11" t="inlineStr">
+        <is>
+          <t>'Polygon Amoy' text visible</t>
+        </is>
+      </c>
+      <c r="H304" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I304" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J304" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K304" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-304</t>
+        </is>
+      </c>
+      <c r="B305" s="6" t="inlineStr">
+        <is>
+          <t>Blockchain Layer</t>
+        </is>
+      </c>
+      <c r="C305" s="11" t="inlineStr">
+        <is>
+          <t>Switching to wrong chain shows alert</t>
+        </is>
+      </c>
+      <c r="D305" s="6" t="inlineStr">
+        <is>
+          <t>Web3</t>
+        </is>
+      </c>
+      <c r="E305" s="11" t="inlineStr">
+        <is>
+          <t>Connect to chain 1 (mainnet)</t>
+        </is>
+      </c>
+      <c r="F305" s="11" t="inlineStr">
+        <is>
+          <t>Alert: Please switch to Amoy 80002</t>
+        </is>
+      </c>
+      <c r="G305" s="11" t="inlineStr">
+        <is>
+          <t>Alert: Please switch to Amoy 80002</t>
+        </is>
+      </c>
+      <c r="H305" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I305" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J305" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K305" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-305</t>
+        </is>
+      </c>
+      <c r="B306" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C306" s="11" t="inlineStr">
+        <is>
+          <t>GET / returns HTTP 200</t>
+        </is>
+      </c>
+      <c r="D306" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E306" s="11" t="inlineStr">
+        <is>
+          <t>HTTP GET /</t>
+        </is>
+      </c>
+      <c r="F306" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="G306" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="H306" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I306" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J306" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K306" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-306</t>
+        </is>
+      </c>
+      <c r="B307" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C307" s="11" t="inlineStr">
+        <is>
+          <t>GET /verify returns HTTP 200</t>
+        </is>
+      </c>
+      <c r="D307" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E307" s="11" t="inlineStr">
+        <is>
+          <t>HTTP GET /verify</t>
+        </is>
+      </c>
+      <c r="F307" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="G307" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="H307" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I307" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J307" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K307" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-307</t>
+        </is>
+      </c>
+      <c r="B308" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C308" s="11" t="inlineStr">
+        <is>
+          <t>GET /login returns HTTP 200</t>
+        </is>
+      </c>
+      <c r="D308" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E308" s="11" t="inlineStr">
+        <is>
+          <t>HTTP GET /login</t>
+        </is>
+      </c>
+      <c r="F308" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="G308" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="H308" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I308" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J308" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K308" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-308</t>
+        </is>
+      </c>
+      <c r="B309" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C309" s="11" t="inlineStr">
+        <is>
+          <t>GET /issuer returns HTTP 200</t>
+        </is>
+      </c>
+      <c r="D309" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E309" s="11" t="inlineStr">
+        <is>
+          <t>HTTP GET /issuer</t>
+        </is>
+      </c>
+      <c r="F309" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="G309" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="H309" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I309" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J309" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K309" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-309</t>
+        </is>
+      </c>
+      <c r="B310" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C310" s="11" t="inlineStr">
+        <is>
+          <t>GET /dashboard returns HTTP 200</t>
+        </is>
+      </c>
+      <c r="D310" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E310" s="11" t="inlineStr">
+        <is>
+          <t>HTTP GET /dashboard</t>
+        </is>
+      </c>
+      <c r="F310" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="G310" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="H310" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I310" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J310" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K310" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-310</t>
+        </is>
+      </c>
+      <c r="B311" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C311" s="11" t="inlineStr">
+        <is>
+          <t>GET /profile returns HTTP 200</t>
+        </is>
+      </c>
+      <c r="D311" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E311" s="11" t="inlineStr">
+        <is>
+          <t>HTTP GET /profile</t>
+        </is>
+      </c>
+      <c r="F311" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="G311" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="H311" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I311" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J311" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K311" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-311</t>
+        </is>
+      </c>
+      <c r="B312" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C312" s="11" t="inlineStr">
+        <is>
+          <t>GET /api/health returns HTTP 200</t>
+        </is>
+      </c>
+      <c r="D312" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E312" s="11" t="inlineStr">
+        <is>
+          <t>HTTP GET /api/health</t>
+        </is>
+      </c>
+      <c r="F312" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="G312" s="11" t="inlineStr">
+        <is>
+          <t>Status 200</t>
+        </is>
+      </c>
+      <c r="H312" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I312" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J312" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K312" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-312</t>
+        </is>
+      </c>
+      <c r="B313" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C313" s="11" t="inlineStr">
+        <is>
+          <t>POST /api/auth/login accepts JSON</t>
+        </is>
+      </c>
+      <c r="D313" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E313" s="11" t="inlineStr">
+        <is>
+          <t>POST with JSON body</t>
+        </is>
+      </c>
+      <c r="F313" s="11" t="inlineStr">
+        <is>
+          <t>Status 200 or 401</t>
+        </is>
+      </c>
+      <c r="G313" s="11" t="inlineStr">
+        <is>
+          <t>Status 200 or 401</t>
+        </is>
+      </c>
+      <c r="H313" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I313" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J313" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K313" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-313</t>
+        </is>
+      </c>
+      <c r="B314" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C314" s="11" t="inlineStr">
+        <is>
+          <t>GET /api/certificates returns JSON array</t>
+        </is>
+      </c>
+      <c r="D314" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E314" s="11" t="inlineStr">
+        <is>
+          <t>GET with valid JWT</t>
+        </is>
+      </c>
+      <c r="F314" s="11" t="inlineStr">
+        <is>
+          <t>Status 200, array body</t>
+        </is>
+      </c>
+      <c r="G314" s="11" t="inlineStr">
+        <is>
+          <t>Status 200, array body</t>
+        </is>
+      </c>
+      <c r="H314" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I314" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J314" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K314" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="6" t="inlineStr">
+        <is>
+          <t>WEB-TC-314</t>
+        </is>
+      </c>
+      <c r="B315" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="C315" s="11" t="inlineStr">
+        <is>
+          <t>404 on undefined /api/unknown</t>
+        </is>
+      </c>
+      <c r="D315" s="6" t="inlineStr">
+        <is>
+          <t>Smoke</t>
+        </is>
+      </c>
+      <c r="E315" s="11" t="inlineStr">
+        <is>
+          <t>HTTP GET /api/unknown</t>
+        </is>
+      </c>
+      <c r="F315" s="11" t="inlineStr">
+        <is>
+          <t>Status 404</t>
+        </is>
+      </c>
+      <c r="G315" s="11" t="inlineStr">
+        <is>
+          <t>Status 404</t>
+        </is>
+      </c>
+      <c r="H315" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I315" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J315" s="6" t="inlineStr">
+        <is>
+          <t>Antigravity Automated Suite</t>
+        </is>
+      </c>
+      <c r="K315" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:57:48</t>
         </is>
       </c>
     </row>
@@ -13542,7 +20142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -13708,14 +20308,14 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Navbar</t>
+          <t>Certificate Card</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>0</v>
@@ -13729,14 +20329,14 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>API Integration</t>
+          <t>QR Scanner Modal</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>0</v>
@@ -13750,14 +20350,14 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>UI/UX Design System</t>
+          <t>Navbar</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>0</v>
@@ -13771,14 +20371,14 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Error Handling</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11" s="17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D11" s="17" t="n">
         <v>0</v>
@@ -13792,14 +20392,14 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Form Validation</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>0</v>
@@ -13813,14 +20413,14 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Auth &amp; Session</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D13" s="17" t="n">
         <v>0</v>
@@ -13834,14 +20434,14 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Web3 Wallet</t>
+          <t>API Integration</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D14" s="17" t="n">
         <v>0</v>
@@ -13855,14 +20455,14 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UI/UX Design System</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D15" s="17" t="n">
         <v>0</v>
@@ -13876,19 +20476,271 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Cross-Browser</t>
+          <t>Batch CSV Issuer</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D16" s="17" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Smoke Tests</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Form Validation</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Blockchain Layer</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Web3 Wallet</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cross-Browser</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>

--- a/automated_test/BlockCertify_2.0_E2E_Security_Load_Report.xlsx
+++ b/automated_test/BlockCertify_2.0_E2E_Security_Load_Report.xlsx
@@ -698,7 +698,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GitHub: github.com/dhanushvk18/Blockcertify2.0  |  Generated: 05 Aug 2026 13:27</t>
+          <t>GitHub: github.com/dhanushvk18/Blockcertify2.0  |  Generated: 05 Aug 2026 13:59</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>2054.84</v>
+        <v>3811.32</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>36.91 ms</t>
+          <t>14.58 ms</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>1.11 ms</t>
+          <t>0.28 ms</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>7806.8 ms</t>
+          <t>2325.06 ms</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>123390</v>
+        <v>230739</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>60</v>
+        <v>60.54</v>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>123390</v>
+        <v>230739</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2054.84</v>
+        <v>3811.32</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>36.91</v>
+        <v>14.58</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1.11</v>
+        <v>0.28</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>7806.8</v>
+        <v>2325.06</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
